--- a/sheets/Libetee_8月勝負日プラン.xlsx
+++ b/sheets/Libetee_8月勝負日プラン.xlsx
@@ -10,6 +10,7 @@
     <sheet name="7月実績" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="8月勝負日_そのままvs攻め" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="グラフ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="用語解説" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="¥#,##0"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +58,11 @@
       <b val="1"/>
       <color rgb="00C0392B"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="14">
@@ -126,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +155,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,6 +326,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1209,17 +1291,17 @@
           <t>そのままパターン</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
+      <c r="E4" s="56" t="n"/>
+      <c r="F4" s="56" t="n"/>
+      <c r="G4" s="57" t="n"/>
       <c r="H4" s="19" t="inlineStr">
         <is>
           <t>攻めパターン（転換率×0.8）</t>
         </is>
       </c>
-      <c r="I4" s="19" t="n"/>
-      <c r="J4" s="19" t="n"/>
-      <c r="K4" s="19" t="n"/>
+      <c r="I4" s="56" t="n"/>
+      <c r="J4" s="56" t="n"/>
+      <c r="K4" s="57" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2088,4 +2170,248 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>用語解説：1アクセス価値</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="59" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
+        </is>
+      </c>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="61" t="n"/>
+      <c r="E3" s="61" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>計算式</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
+        </is>
+      </c>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t>例（かぶり日・7月実績）</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>使い方①（広告判断）</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+        </is>
+      </c>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="59" t="inlineStr">
+        <is>
+          <t>使い方②（増額試算）</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B10" s="62" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="C10" s="62" t="inlineStr">
+        <is>
+          <t>広告単価(メタ)</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>倍率</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="inlineStr">
+        <is>
+          <t>読み方</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="63" t="inlineStr">
+        <is>
+          <t>かぶり日（イベント×5と0）</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" s="64" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="65" t="n">
+        <v>7.916666666666667</v>
+      </c>
+      <c r="E11" s="66" t="inlineStr">
+        <is>
+          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="67" t="inlineStr">
+        <is>
+          <t>ワンダフルデー</t>
+        </is>
+      </c>
+      <c r="B12" s="68" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="E12" s="70" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="71" t="inlineStr">
+        <is>
+          <t>5と0のつく日（単独）</t>
+        </is>
+      </c>
+      <c r="B13" s="72" t="n">
+        <v>61</v>
+      </c>
+      <c r="C13" s="72" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" s="73" t="n">
+        <v>5.083333333333333</v>
+      </c>
+      <c r="E13" s="74" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="75" t="inlineStr">
+        <is>
+          <t>マラソン通常</t>
+        </is>
+      </c>
+      <c r="B14" s="76" t="n">
+        <v>46</v>
+      </c>
+      <c r="C14" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="77" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="E14" s="78" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>平日</t>
+        </is>
+      </c>
+      <c r="B15" s="80" t="n">
+        <v>41</v>
+      </c>
+      <c r="C15" s="80" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="81" t="n">
+        <v>3.416666666666667</v>
+      </c>
+      <c r="E15" s="82" t="inlineStr">
+        <is>
+          <t>それでも3.4倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sheets/Libetee_8月勝負日プラン.xlsx
+++ b/sheets/Libetee_8月勝負日プラン.xlsx
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1281,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>スーツケース広告の設定。そのまま＝平日2万/イベント3万・転換率7月実績。攻め＝平日3万/イベント5万・転換率×0.8。広告費＝アクセス×¥12(メタ実績単価)。売上/日＝SC+FAN(FAN据え置き)。</t>
+          <t>スーツケース広告の設定。そのまま＝平日2万/イベント3万・転換率7月実績。攻め＝平日3万/イベント5万・転換率×0.8。広告費＝SCアクセス×¥10（アクセス単価統一）。ハンディファンは¥8/アクセス・据え置きのため両パターン共通＝差額に影響なし。売上/日＝SC+FAN。</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         <v>0.001345398239907378</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G6" s="24" t="n">
         <v>1199910</v>
@@ -1403,7 +1403,7 @@
         <v>0.001076318591925903</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>1596803</v>
@@ -1436,7 +1436,7 @@
         <v>0.001342722645169273</v>
       </c>
       <c r="F7" s="30" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>1357078</v>
@@ -1448,7 +1448,7 @@
         <v>0.001074178116135419</v>
       </c>
       <c r="J7" s="30" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K7" s="30" t="n">
         <v>1753181</v>
@@ -1481,7 +1481,7 @@
         <v>0.003733655419830527</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G8" s="36" t="n">
         <v>3979792</v>
@@ -1493,7 +1493,7 @@
         <v>0.002986924335864422</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K8" s="36" t="n">
         <v>5081220</v>
@@ -1526,7 +1526,7 @@
         <v>0.001342722645169273</v>
       </c>
       <c r="F9" s="30" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>1357078</v>
@@ -1538,7 +1538,7 @@
         <v>0.001074178116135419</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K9" s="30" t="n">
         <v>1753181</v>
@@ -1571,7 +1571,7 @@
         <v>0.003733655419830527</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G10" s="36" t="n">
         <v>3979792</v>
@@ -1583,7 +1583,7 @@
         <v>0.002986924335864422</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K10" s="36" t="n">
         <v>5081220</v>
@@ -1616,7 +1616,7 @@
         <v>0.00126895071306332</v>
       </c>
       <c r="F11" s="42" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G11" s="42" t="n">
         <v>1647756</v>
@@ -1628,7 +1628,7 @@
         <v>0.001015160570450656</v>
       </c>
       <c r="J11" s="42" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K11" s="42" t="n">
         <v>2022097</v>
@@ -1661,7 +1661,7 @@
         <v>0.00126895071306332</v>
       </c>
       <c r="F12" s="42" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G12" s="42" t="n">
         <v>1647756</v>
@@ -1673,7 +1673,7 @@
         <v>0.001015160570450656</v>
       </c>
       <c r="J12" s="42" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K12" s="42" t="n">
         <v>2022097</v>
@@ -1706,7 +1706,7 @@
         <v>0.001342722645169273</v>
       </c>
       <c r="F13" s="30" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G13" s="30" t="n">
         <v>1357078</v>
@@ -1718,7 +1718,7 @@
         <v>0.001074178116135419</v>
       </c>
       <c r="J13" s="30" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K13" s="30" t="n">
         <v>1753181</v>
@@ -1751,7 +1751,7 @@
         <v>0.003733655419830527</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G14" s="36" t="n">
         <v>3979792</v>
@@ -1763,7 +1763,7 @@
         <v>0.002986924335864422</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K14" s="36" t="n">
         <v>5081220</v>
@@ -1796,7 +1796,7 @@
         <v>0.001342722645169273</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G15" s="30" t="n">
         <v>1357078</v>
@@ -1808,7 +1808,7 @@
         <v>0.001074178116135419</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K15" s="30" t="n">
         <v>1753181</v>
@@ -1841,7 +1841,7 @@
         <v>0.00126895071306332</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="G16" s="42" t="n">
         <v>1647756</v>
@@ -1853,7 +1853,7 @@
         <v>0.001015160570450656</v>
       </c>
       <c r="J16" s="42" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="K16" s="42" t="n">
         <v>2022097</v>
@@ -1886,7 +1886,7 @@
         <v>0.001516042653417946</v>
       </c>
       <c r="F17" s="48" t="n">
-        <v>240000</v>
+        <v>200000</v>
       </c>
       <c r="G17" s="48" t="n">
         <v>1158307</v>
@@ -1898,7 +1898,7 @@
         <v>0.001212834122734357</v>
       </c>
       <c r="J17" s="48" t="n">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="K17" s="48" t="n">
         <v>1337200</v>
@@ -1921,7 +1921,7 @@
       <c r="D18" s="50" t="n"/>
       <c r="E18" s="50" t="n"/>
       <c r="F18" s="51" t="n">
-        <v>9120000</v>
+        <v>7600000</v>
       </c>
       <c r="G18" s="51" t="n">
         <v>47273319</v>
@@ -1929,7 +1929,7 @@
       <c r="H18" s="50" t="n"/>
       <c r="I18" s="50" t="n"/>
       <c r="J18" s="51" t="n">
-        <v>14520000</v>
+        <v>12100000</v>
       </c>
       <c r="K18" s="51" t="n">
         <v>57911421</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="D22" s="55" t="n">
-        <v>5400000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="23">
@@ -1973,18 +1973,25 @@
         </is>
       </c>
       <c r="D23" s="54" t="n">
-        <v>5238102</v>
+        <v>6138102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>増分ROAS＝売上差額÷広告費差額＝2.0倍（転換率×0.8の保守前提。×0.9なら3.1倍）</t>
+          <t>増分ROAS＝売上差額÷広告費差額＝2.4倍（転換率×0.8の保守前提。×0.9なら3.7倍）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>【補足】アクセス単価の前提：スーツケース＝¥10/アクセス、ハンディファン＝¥8/アクセスで統一。FANはアクセス据え置きのため広告費も両パターン同額（差額計算に影響しない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>★勝負日の頂点は8/5・8/10・8/25のかぶり3日：攻めで1日¥508万（+¥110万/日）。在庫最厚で臨むこと。</t>
         </is>
@@ -2160,10 +2167,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9120000</v>
+        <v>7600000</v>
       </c>
       <c r="J14" t="n">
-        <v>14520000</v>
+        <v>12100000</v>
       </c>
     </row>
   </sheetData>
@@ -2178,20 +2185,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="58" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値</t>
+          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2255,7 @@
       </c>
       <c r="B6" s="60" t="inlineStr">
         <is>
-          <t>メタ広告のアクセス単価(約¥12)と比べる。¥12で1人連れてきて、その日の価値が¥95なら8倍で返る計算</t>
+          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
         </is>
       </c>
       <c r="C6" s="61" t="n"/>
@@ -2270,142 +2277,158 @@
       <c r="D7" s="61" t="n"/>
       <c r="E7" s="61" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="53" t="inlineStr">
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>★アクセス単価の統一前提</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
+        </is>
+      </c>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="62" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="62" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B10" s="62" t="inlineStr">
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>1アクセス価値</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
-        <is>
-          <t>広告単価(メタ)</t>
-        </is>
-      </c>
-      <c r="D10" s="62" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>SC単価</t>
+        </is>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E10" s="62" t="inlineStr">
+      <c r="E11" s="62" t="inlineStr">
         <is>
           <t>読み方</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="63" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>かぶり日（イベント×5と0）</t>
         </is>
       </c>
-      <c r="B11" s="64" t="n">
+      <c r="B12" s="64" t="n">
         <v>95</v>
       </c>
-      <c r="C11" s="64" t="n">
-        <v>12</v>
-      </c>
-      <c r="D11" s="65" t="n">
-        <v>7.916666666666667</v>
-      </c>
-      <c r="E11" s="66" t="inlineStr">
-        <is>
-          <t>¥12仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="C12" s="64" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="67" t="inlineStr">
         <is>
           <t>ワンダフルデー</t>
         </is>
       </c>
-      <c r="B12" s="68" t="n">
+      <c r="B13" s="68" t="n">
         <v>94</v>
       </c>
-      <c r="C12" s="68" t="n">
-        <v>12</v>
-      </c>
-      <c r="D12" s="69" t="n">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="E12" s="70" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="71" t="inlineStr">
+      <c r="C13" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E13" s="70" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="71" t="inlineStr">
         <is>
           <t>5と0のつく日（単独）</t>
         </is>
       </c>
-      <c r="B13" s="72" t="n">
+      <c r="B14" s="72" t="n">
         <v>61</v>
       </c>
-      <c r="C13" s="72" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" s="73" t="n">
-        <v>5.083333333333333</v>
-      </c>
-      <c r="E13" s="74" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="75" t="inlineStr">
+      <c r="C14" s="72" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="73" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E14" s="74" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>マラソン通常</t>
         </is>
       </c>
-      <c r="B14" s="76" t="n">
+      <c r="B15" s="76" t="n">
         <v>46</v>
       </c>
-      <c r="C14" s="76" t="n">
-        <v>12</v>
-      </c>
-      <c r="D14" s="77" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="E14" s="78" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="79" t="inlineStr">
+      <c r="C15" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="77" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E15" s="78" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>平日</t>
         </is>
       </c>
-      <c r="B15" s="80" t="n">
+      <c r="B16" s="80" t="n">
         <v>41</v>
       </c>
-      <c r="C15" s="80" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="81" t="n">
-        <v>3.416666666666667</v>
-      </c>
-      <c r="E15" s="82" t="inlineStr">
-        <is>
-          <t>それでも3.4倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値は別掲（平日¥45／かぶり日¥110）。転換率・客単価は2026年7月実績（公式カレンダー分類）。</t>
+      <c r="C16" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="81" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E16" s="82" t="inlineStr">
+        <is>
+          <t>それでも4.1倍。広告を切らない理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>

--- a/sheets/Libetee_8月勝負日プラン.xlsx
+++ b/sheets/Libetee_8月勝負日プラン.xlsx
@@ -65,7 +65,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +130,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE2DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -203,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -357,6 +362,15 @@
     <xf numFmtId="164" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2185,255 +2199,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="58" t="inlineStr">
         <is>
-          <t>用語解説：1アクセス価値 ／ アクセス単価の前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="59" t="inlineStr">
-        <is>
-          <t>定義</t>
-        </is>
-      </c>
-      <c r="B3" s="60" t="inlineStr">
-        <is>
-          <t>お客さん1人がページに来たとき、平均していくら売上になるか</t>
-        </is>
-      </c>
-      <c r="C3" s="61" t="n"/>
-      <c r="D3" s="61" t="n"/>
-      <c r="E3" s="61" t="n"/>
+          <t>用語解説（お店にたとえた、やさしい版）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>用語</t>
+        </is>
+      </c>
+      <c r="B3" s="62" t="inlineStr">
+        <is>
+          <t>お店で言うと</t>
+        </is>
+      </c>
+      <c r="C3" s="62" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="D3" s="62" t="inlineStr">
+        <is>
+          <t>この店の数字(7月実績)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
-        <is>
-          <t>計算式</t>
+      <c r="A4" s="83" t="inlineStr">
+        <is>
+          <t>アクセス数</t>
         </is>
       </c>
       <c r="B4" s="60" t="inlineStr">
         <is>
-          <t>1アクセス価値 ＝ 転換率 × 客単価</t>
-        </is>
-      </c>
-      <c r="C4" s="61" t="n"/>
-      <c r="D4" s="61" t="n"/>
-      <c r="E4" s="61" t="n"/>
+          <t>お店に入ってきた人数</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>ページを見に来た人の数（買わない人も含む）</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>かぶり日 約4.2万人/日</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="59" t="inlineStr">
-        <is>
-          <t>例（かぶり日・7月実績）</t>
+      <c r="A5" s="83" t="inlineStr">
+        <is>
+          <t>転換率</t>
         </is>
       </c>
       <c r="B5" s="60" t="inlineStr">
         <is>
-          <t>転換率0.73% × 客単価¥13,048 ≒ ¥95。1,000人来たら約7人が買い、売上約¥95,000 → 1人あたり¥95</t>
-        </is>
-      </c>
-      <c r="C5" s="61" t="n"/>
-      <c r="D5" s="61" t="n"/>
-      <c r="E5" s="61" t="n"/>
+          <t>入った人のうち買った人の割合</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>100人入店して1人買えば1%</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>かぶり日0.73%＝1,000人中7人</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="59" t="inlineStr">
-        <is>
-          <t>使い方①（広告判断）</t>
+      <c r="A6" s="83" t="inlineStr">
+        <is>
+          <t>客単価</t>
         </is>
       </c>
       <c r="B6" s="60" t="inlineStr">
         <is>
-          <t>アクセス単価と比べる。¥10で1人連れてきて、その日の価値が¥95なら9.5倍で返る計算</t>
-        </is>
-      </c>
-      <c r="C6" s="61" t="n"/>
-      <c r="D6" s="61" t="n"/>
-      <c r="E6" s="61" t="n"/>
+          <t>買った人1人の平均支払額</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>レジ1回の平均金額</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>かぶり日¥13,048</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="59" t="inlineStr">
-        <is>
-          <t>使い方②（増額試算）</t>
-        </is>
-      </c>
-      <c r="B7" s="60" t="inlineStr">
-        <is>
-          <t>追加売上 ＝ 増やすアクセス数 × 1アクセス価値。転換率×0.8のシナリオは価値を2割引きで見積もったもの</t>
-        </is>
-      </c>
-      <c r="C7" s="61" t="n"/>
-      <c r="D7" s="61" t="n"/>
-      <c r="E7" s="61" t="n"/>
+      <c r="A7" s="84" t="inlineStr">
+        <is>
+          <t>1アクセス価値</t>
+        </is>
+      </c>
+      <c r="B7" s="85" t="inlineStr">
+        <is>
+          <t>入店客1人あたりの平均売上</t>
+        </is>
+      </c>
+      <c r="C7" s="85" t="inlineStr">
+        <is>
+          <t>転換率×客単価。1人来店するたび平均いくら売れるか</t>
+        </is>
+      </c>
+      <c r="D7" s="85" t="inlineStr">
+        <is>
+          <t>かぶり日¥95／平日¥41</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="59" t="inlineStr">
-        <is>
-          <t>★アクセス単価の統一前提</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="inlineStr">
-        <is>
-          <t>スーツケース ¥10/アクセス ／ ハンディファン ¥8/アクセス（社長指定・全シート共通）</t>
-        </is>
-      </c>
-      <c r="C8" s="61" t="n"/>
-      <c r="D8" s="61" t="n"/>
-      <c r="E8" s="61" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="53" t="inlineStr">
-        <is>
-          <t>セグメント別 1アクセス価値（7月公式実績・店舗全体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="62" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B11" s="62" t="inlineStr">
-        <is>
-          <t>1アクセス価値</t>
-        </is>
-      </c>
-      <c r="C11" s="62" t="inlineStr">
-        <is>
-          <t>SC単価</t>
-        </is>
-      </c>
-      <c r="D11" s="62" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
+        <is>
+          <t>アクセス単価</t>
+        </is>
+      </c>
+      <c r="B8" s="85" t="inlineStr">
+        <is>
+          <t>1人を連れてくるチラシ代</t>
+        </is>
+      </c>
+      <c r="C8" s="85" t="inlineStr">
+        <is>
+          <t>広告費÷アクセス数</t>
+        </is>
+      </c>
+      <c r="D8" s="85" t="inlineStr">
+        <is>
+          <t>スーツケース¥10／ファン¥8（統一）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="83" t="inlineStr">
         <is>
           <t>倍率</t>
         </is>
       </c>
-      <c r="E11" s="62" t="inlineStr">
-        <is>
-          <t>読み方</t>
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>チラシ代の何倍売れるか</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>1アクセス価値÷アクセス単価</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="inlineStr">
+        <is>
+          <t>かぶり日9.5倍／平日4.1倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="83" t="inlineStr">
+        <is>
+          <t>かぶり日</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>特売日が2つ重なった日</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>お買い物マラソン×5と0のつく日</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>8/5・8/10・8/25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="63" t="inlineStr">
-        <is>
-          <t>かぶり日（イベント×5と0）</t>
-        </is>
-      </c>
-      <c r="B12" s="64" t="n">
-        <v>95</v>
-      </c>
-      <c r="C12" s="64" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="65" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E12" s="66" t="inlineStr">
-        <is>
-          <t>¥10仕入→¥95売上。最優先で広告を張る日</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="67" t="inlineStr">
-        <is>
-          <t>ワンダフルデー</t>
-        </is>
-      </c>
-      <c r="B13" s="68" t="n">
-        <v>94</v>
-      </c>
-      <c r="C13" s="68" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="69" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="E13" s="70" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="71" t="inlineStr">
-        <is>
-          <t>5と0のつく日（単独）</t>
-        </is>
-      </c>
-      <c r="B14" s="72" t="n">
-        <v>61</v>
-      </c>
-      <c r="C14" s="72" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="73" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="E14" s="74" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="75" t="inlineStr">
-        <is>
-          <t>マラソン通常</t>
-        </is>
-      </c>
-      <c r="B15" s="76" t="n">
-        <v>46</v>
-      </c>
-      <c r="C15" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="77" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E15" s="78" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="79" t="inlineStr">
-        <is>
-          <t>平日</t>
-        </is>
-      </c>
-      <c r="B16" s="80" t="n">
-        <v>41</v>
-      </c>
-      <c r="C16" s="80" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="81" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E16" s="82" t="inlineStr">
-        <is>
-          <t>それでも4.1倍。広告を切らない理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>※スーツケースのみの価値：平日¥45／かぶり日¥110。ハンディファンの広告費は¥8/アクセス（据え置き）。</t>
-        </is>
-      </c>
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>商売の流れ</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>広告費を払う(¥10で1人) → お客さんが来る(アクセス) → 一部が買う(転換率) → 売上(客単価)</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="61" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>かぶり日の例</t>
+        </is>
+      </c>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>¥10×1,000人=広告費¥1万 → 1,000人来店 → 7人購入 → 売上¥95,000（＝9.5倍）。平日は同じ¥1万で¥41,000（4.1倍）</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B5:E5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
